--- a/data/trans_orig/IP16B01-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16B01-Provincia-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>3638</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3847</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8283</t>
+          <t>8030</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19956</t>
+          <t>20512</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>3996</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>2936</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22676</t>
+          <t>21928</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>62573</t>
+          <t>62854</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>4704</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>120598</t>
+          <t>120580</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>264198</t>
+          <t>264520</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8032</t>
+          <t>8144</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12362</t>
+          <t>12335</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6992</t>
+          <t>6864</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16850</t>
+          <t>16932</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22135</t>
+          <t>22116</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>524</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2869</t>
+          <t>2997</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>604</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,48%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8765</t>
+          <t>8269</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13267</t>
+          <t>13271</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11245</t>
+          <t>10672</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21877</t>
+          <t>21806</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27223</t>
+          <t>27655</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>622</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>5624</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1686</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7032</t>
+          <t>7103</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,57%</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14790</t>
+          <t>14157</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24600</t>
+          <t>25048</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8373</t>
+          <t>8398</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14209</t>
+          <t>14230</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17324</t>
+          <t>17040</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24200</t>
+          <t>24085</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7150</t>
+          <t>7125</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>8667</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>33,71%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11544</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4481</t>
+          <t>4474</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13914</t>
+          <t>14047</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20353</t>
+          <t>20409</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,26%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>696</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5019</t>
+          <t>5266</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7969</t>
+          <t>7836</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5676</t>
+          <t>5669</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>7196</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10285</t>
+          <t>10551</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15760</t>
+          <t>15759</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>472</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3059</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>728</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>36,0%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10425</t>
+          <t>10007</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15418</t>
+          <t>15410</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10940</t>
+          <t>10866</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23602</t>
+          <t>22937</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29031</t>
+          <t>29025</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>689</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5674</t>
+          <t>6092</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>3393</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>7420</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>24,44%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5787</t>
+          <t>5649</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10464</t>
+          <t>10454</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16217</t>
+          <t>16330</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22326</t>
+          <t>22335</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>667</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5334</t>
+          <t>5472</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>648</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6766</t>
+          <t>6653</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>28,95%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>73996</t>
+          <t>73677</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>86422</t>
+          <t>86225</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>87123</t>
+          <t>87037</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>96011</t>
+          <t>95751</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>164724</t>
+          <t>165258</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>179957</t>
+          <t>180086</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,34%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11785</t>
+          <t>11982</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24211</t>
+          <t>24530</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11824</t>
+          <t>11910</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>17196</t>
+          <t>17067</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>32429</t>
+          <t>31895</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1537</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6222</t>
+          <t>6318</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5598</t>
+          <t>5692</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10718</t>
+          <t>10855</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8948</t>
+          <t>8814</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16007</t>
+          <t>15932</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,23%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1589</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>709</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10427</t>
+          <t>10561</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>54,51%</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14007</t>
+          <t>13792</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18967</t>
+          <t>19015</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24193</t>
+          <t>24551</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29614</t>
+          <t>29611</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>595</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>5818</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>658</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>5718</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -8099,7 +8099,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6154</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8252,7 +8252,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3668</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>34,65%</t>
         </is>
       </c>
     </row>
@@ -8407,7 +8407,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8348</t>
+          <t>8707</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9214</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14617</t>
+          <t>14619</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20850</t>
+          <t>20447</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26833</t>
+          <t>26469</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>93,32%</t>
         </is>
       </c>
     </row>
@@ -8525,7 +8525,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4744</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>654</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6059</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7514</t>
+          <t>7917</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>976</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>622</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2297</t>
+          <t>2334</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>7451</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,89%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>615</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9246,7 +9246,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>747</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>5864</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>71,54%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>3874</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8238</t>
+          <t>8254</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10862</t>
+          <t>10927</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16228</t>
+          <t>16270</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>93,05%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>6559</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,51%</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6738</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7542</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>15859</t>
+          <t>16075</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9912,7 +9912,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9932,7 +9932,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4878</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>56439</t>
+          <t>55837</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>67099</t>
+          <t>67045</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>53488</t>
+          <t>53546</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>62610</t>
+          <t>62516</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>113939</t>
+          <t>113767</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>127644</t>
+          <t>127868</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,31%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9349</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>19955</t>
+          <t>20557</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>13296</t>
+          <t>13238</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>15534</t>
+          <t>15310</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>29239</t>
+          <t>29411</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
